--- a/DataTables/DetailText/剧情/000_03如何出书.xlsx
+++ b/DataTables/DetailText/剧情/000_03如何出书.xlsx
@@ -1,35 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6EFC8A6-D4FB-4F57-AEEA-E64E3F98BB29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72C4F23C-6E14-4F63-A1C1-5BB71539D969}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
     <sheet name="StoryLine" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -496,7 +483,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -707,7 +694,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T20"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="7.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.25" customWidth="1"/>
@@ -725,7 +712,7 @@
     <col min="19" max="20" width="10.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="21" customFormat="1" ht="18">
+    <row r="1" spans="1:20" s="21" customFormat="1">
       <c r="A1" s="16" t="s">
         <v>14</v>
       </c>
@@ -787,7 +774,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:20" s="21" customFormat="1" ht="18">
+    <row r="2" spans="1:20" s="21" customFormat="1">
       <c r="A2" s="25" t="s">
         <v>49</v>
       </c>
@@ -798,7 +785,7 @@
         <v>33</v>
       </c>
       <c r="D2" s="23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2" s="23"/>
       <c r="F2" s="23"/>
